--- a/Experiments data/K Size/K_Size_4elt_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_4elt_Graph.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AF3C694-0320-46A5-A8BA-B829BCB56773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30FD100-DFA2-4E42-B391-DD6A0E6B5456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -279,7 +279,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -317,14 +317,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -334,10 +334,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -684,7 +680,7 @@
                   <c:v>498.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6317.6</c:v>
+                  <c:v>732</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>9273.6</c:v>
@@ -777,7 +773,7 @@
                   <c:v>388.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3524.8</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5641.2</c:v>
@@ -1770,7 +1766,7 @@
                   <c:v>-0.44322132097334882</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-9.4492226265299362</c:v>
+                  <c:v>-0.2107178299702282</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>-7.8387342737323671</c:v>
@@ -1857,7 +1853,7 @@
                   <c:v>-0.12572421784472779</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-4.8299702282500832</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>-4.3766679374761726</c:v>
@@ -3553,7 +3549,7 @@
                   <c:v>3.0064000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.6419999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>5.2645999999999997</c:v>
@@ -12265,10 +12261,7 @@
         <v>604</v>
       </c>
       <c r="H25">
-        <v>7354</v>
-      </c>
-      <c r="I25">
-        <v>4490</v>
+        <v>732</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -12293,12 +12286,6 @@
       <c r="G26">
         <v>586</v>
       </c>
-      <c r="H26">
-        <v>5805</v>
-      </c>
-      <c r="I26">
-        <v>3772</v>
-      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -12322,12 +12309,6 @@
       <c r="G27">
         <v>584</v>
       </c>
-      <c r="H27">
-        <v>6699</v>
-      </c>
-      <c r="I27">
-        <v>3379</v>
-      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -12351,12 +12332,6 @@
       <c r="G28">
         <v>649</v>
       </c>
-      <c r="H28">
-        <v>6266</v>
-      </c>
-      <c r="I28">
-        <v>3912</v>
-      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -12379,12 +12354,6 @@
       </c>
       <c r="G29">
         <v>600</v>
-      </c>
-      <c r="H29">
-        <v>5464</v>
-      </c>
-      <c r="I29">
-        <v>2071</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -12729,11 +12698,11 @@
       </c>
       <c r="H57">
         <f>AVERAGE(H25:H29)</f>
-        <v>6317.6</v>
-      </c>
-      <c r="I57">
+        <v>732</v>
+      </c>
+      <c r="I57" t="e">
         <f>AVERAGE(I25:I29)</f>
-        <v>3524.8</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -12846,11 +12815,11 @@
       </c>
       <c r="H68" s="12">
         <f t="shared" si="6"/>
-        <v>-9.4492226265299362</v>
-      </c>
-      <c r="I68" s="12">
+        <v>-0.2107178299702282</v>
+      </c>
+      <c r="I68" s="12" t="e">
         <f t="shared" si="7"/>
-        <v>-4.8299702282500832</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="69" spans="5:10" x14ac:dyDescent="0.25">
@@ -13406,6 +13375,9 @@
       <c r="G24">
         <v>0.85599999999999998</v>
       </c>
+      <c r="H24">
+        <v>3.6419999999999999</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -13836,9 +13808,9 @@
         <f t="shared" si="2"/>
         <v>1.2193999999999998</v>
       </c>
-      <c r="H57" t="e">
+      <c r="H57">
         <f>AVERAGE(H24:H28)</f>
-        <v>#DIV/0!</v>
+        <v>3.6419999999999999</v>
       </c>
       <c r="I57" t="e">
         <f>AVERAGE(I24:I28)</f>
@@ -14116,11 +14088,11 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -14186,11 +14158,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
@@ -14226,7 +14198,7 @@
       <c r="E21" s="5">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="5">
         <v>6.1920000000000003E-2</v>
       </c>
     </row>
@@ -14246,7 +14218,7 @@
       <c r="E22" s="5">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="5">
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
@@ -14266,7 +14238,7 @@
       <c r="E23" s="5">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="5">
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
@@ -14286,7 +14258,7 @@
       <c r="E24" s="5">
         <v>0.1017</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="5">
         <v>6.1920000000000003E-2</v>
       </c>
     </row>
@@ -14306,7 +14278,7 @@
       <c r="E25" s="5">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="5">
         <v>7.5999999999999998E-2</v>
       </c>
     </row>
@@ -14523,11 +14495,11 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
@@ -14569,7 +14541,7 @@
       <c r="F40" s="5">
         <v>0.1152</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="5">
         <v>0.28101999999999999</v>
       </c>
     </row>
@@ -14592,7 +14564,7 @@
       <c r="F41" s="5">
         <v>2.6669999999999999E-2</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="5">
         <v>0.23186999999999999</v>
       </c>
     </row>
@@ -14615,7 +14587,7 @@
       <c r="F42" s="5">
         <v>7.9829999999999998E-2</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="5">
         <v>0.35732000000000003</v>
       </c>
     </row>
@@ -14638,7 +14610,7 @@
       <c r="F43" s="5">
         <v>9.9860000000000004E-2</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="5">
         <v>0.33110000000000001</v>
       </c>
     </row>
@@ -14661,7 +14633,7 @@
       <c r="F44" s="5">
         <v>0.12235</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="5">
         <v>0.25290000000000001</v>
       </c>
     </row>
@@ -14821,11 +14793,11 @@
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="8"/>
@@ -15146,11 +15118,11 @@
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
+      <c r="B75" s="18"/>
+      <c r="C75" s="18"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="8"/>
@@ -15401,11 +15373,11 @@
     </row>
     <row r="94" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="19" t="s">
+      <c r="A95" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B95" s="19"/>
-      <c r="C95" s="19"/>
+      <c r="B95" s="17"/>
+      <c r="C95" s="17"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
@@ -15521,12 +15493,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A75:C75"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -15537,6 +15503,12 @@
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A75:C75"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15736,7 +15708,7 @@
       <c r="I8" s="6">
         <v>2</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="6">
         <v>2</v>
       </c>
     </row>
@@ -15768,7 +15740,7 @@
       <c r="I9" s="6">
         <v>2</v>
       </c>
-      <c r="J9" s="24">
+      <c r="J9" s="6">
         <v>2</v>
       </c>
     </row>

--- a/Experiments data/K Size/K_Size_4elt_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_4elt_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30FD100-DFA2-4E42-B391-DD6A0E6B5456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9519144-CC35-44F9-8FBA-796B7C95D859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -116,16 +116,7 @@
     <t>Deep Multilevel, ε= 0.0</t>
   </si>
   <si>
-    <t>Deep Multilevel, ε = 0.05</t>
-  </si>
-  <si>
     <t>K = 8, Graph = 4elt, Contraction = 70%, Cardinality Sizes = [ 654, 850, 1105, 1437, 1868, 2429, 3157, 4106] at f = 0.3, CL= 2341</t>
-  </si>
-  <si>
-    <t>Deep Multilevel, ε = 5</t>
-  </si>
-  <si>
-    <t>Deep Multilevel, ε= 0</t>
   </si>
   <si>
     <t>(B2−C2)/B2</t>
@@ -141,6 +132,15 @@
   </si>
   <si>
     <t>Deep Multilevel, ε = 1561</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 50</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 780</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε= 0.0</t>
   </si>
 </sst>
 </file>
@@ -317,14 +317,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -677,13 +677,13 @@
                   <c:v>182.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>498.2</c:v>
+                  <c:v>458.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>732</c:v>
+                  <c:v>792.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9273.6</c:v>
+                  <c:v>1375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -773,10 +773,10 @@
                   <c:v>388.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>720.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5641.2</c:v>
+                  <c:v>1270.5999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1703,7 +1703,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1763,13 +1763,13 @@
                   <c:v>-0.31936416184971089</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.44322132097334882</c:v>
+                  <c:v>-0.32734646581691773</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.2107178299702282</c:v>
+                  <c:v>-0.31028779358253394</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-7.8387342737323671</c:v>
+                  <c:v>-0.31052230270682418</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1790,7 +1790,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 780</c:v>
+                  <c:v>Deep NUGP, ε = 780</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1853,10 +1853,10 @@
                   <c:v>-0.12572421784472779</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-0.19120079391333117</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.3766679374761726</c:v>
+                  <c:v>-0.21101791841402959</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1965,7 +1965,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1997,7 +1997,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -2464,16 +2464,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>40.6</c:v>
+                  <c:v>19.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>164.4</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>329.2</c:v>
+                  <c:v>107</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>333.4</c:v>
+                  <c:v>188.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2565,7 +2565,7 @@
                   <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>248</c:v>
+                  <c:v>180.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3480,7 +3480,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3549,10 +3549,10 @@
                   <c:v>3.0064000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.6419999999999999</c:v>
+                  <c:v>3.8542000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.2645999999999997</c:v>
+                  <c:v>3.8741999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3573,7 +3573,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 0.05</c:v>
+                  <c:v>Deep NUGP, ε = 780</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3642,7 +3642,7 @@
                   <c:v>3.2231999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.7851999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3.5635999999999997</c:v>
@@ -4680,7 +4680,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep Multilevel, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4767,7 +4767,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep Multilevel, ε = 780</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4830,10 +4830,10 @@
                   <c:v>8.8782E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9528200000000004E-2</c:v>
+                  <c:v>0.266598</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.7041400000000002E-2</c:v>
+                  <c:v>0.22079799999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5504,7 +5504,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5591,7 +5591,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 780</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5654,10 +5654,10 @@
                   <c:v>7.8972000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.4559999999999994E-2</c:v>
+                  <c:v>0.212426</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.0662000000000006E-2</c:v>
+                  <c:v>0.24162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6225,7 +6225,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep Multilevel, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6294,7 +6294,7 @@
                   <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>476.6</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>598.4</c:v>
@@ -6318,7 +6318,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep Multilevel, ε = 780</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6387,7 +6387,7 @@
                   <c:v>4.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>206.6</c:v>
+                  <c:v>31.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>343.4</c:v>
@@ -11056,16 +11056,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>119061</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>52386</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11356,7 +11356,7 @@
             <v>2</v>
           </cell>
           <cell r="H51">
-            <v>40.6</v>
+            <v>19.600000000000001</v>
           </cell>
           <cell r="I51">
             <v>27.8</v>
@@ -11385,7 +11385,7 @@
             <v>11.8</v>
           </cell>
           <cell r="H52">
-            <v>164.4</v>
+            <v>84</v>
           </cell>
           <cell r="I52">
             <v>40.799999999999997</v>
@@ -11414,7 +11414,7 @@
             <v>16</v>
           </cell>
           <cell r="H53">
-            <v>329.2</v>
+            <v>107</v>
           </cell>
           <cell r="I53">
             <v>119</v>
@@ -11443,10 +11443,10 @@
             <v>78.8</v>
           </cell>
           <cell r="H54">
-            <v>333.4</v>
+            <v>188.4</v>
           </cell>
           <cell r="I54">
-            <v>248</v>
+            <v>180.4</v>
           </cell>
         </row>
       </sheetData>
@@ -11767,7 +11767,7 @@
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
       <c r="I1" s="13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -11781,7 +11781,7 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11808,10 +11808,10 @@
         <v>24</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -12020,10 +12020,10 @@
         <v>24</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -12113,7 +12113,7 @@
         <v>342</v>
       </c>
       <c r="H16">
-        <v>623</v>
+        <v>423</v>
       </c>
       <c r="I16">
         <v>435</v>
@@ -12188,7 +12188,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -12232,10 +12232,10 @@
         <v>24</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -12261,7 +12261,10 @@
         <v>604</v>
       </c>
       <c r="H25">
-        <v>732</v>
+        <v>750</v>
+      </c>
+      <c r="I25">
+        <v>708</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -12286,6 +12289,12 @@
       <c r="G26">
         <v>586</v>
       </c>
+      <c r="H26">
+        <v>782</v>
+      </c>
+      <c r="I26">
+        <v>737</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -12309,6 +12318,12 @@
       <c r="G27">
         <v>584</v>
       </c>
+      <c r="H27">
+        <v>805</v>
+      </c>
+      <c r="I27">
+        <v>670</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -12332,6 +12347,12 @@
       <c r="G28">
         <v>649</v>
       </c>
+      <c r="H28">
+        <v>814</v>
+      </c>
+      <c r="I28">
+        <v>601</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -12354,6 +12375,12 @@
       </c>
       <c r="G29">
         <v>600</v>
+      </c>
+      <c r="H29">
+        <v>810</v>
+      </c>
+      <c r="I29">
+        <v>885</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -12402,10 +12429,10 @@
         <v>24</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -12431,10 +12458,10 @@
         <v>1081</v>
       </c>
       <c r="H36">
-        <v>10599</v>
+        <v>1236</v>
       </c>
       <c r="I36">
-        <v>5162</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -12460,10 +12487,10 @@
         <v>984</v>
       </c>
       <c r="H37">
-        <v>8325</v>
+        <v>1336</v>
       </c>
       <c r="I37">
-        <v>5369</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -12489,10 +12516,10 @@
         <v>1060</v>
       </c>
       <c r="H38">
-        <v>10821</v>
+        <v>1380</v>
       </c>
       <c r="I38">
-        <v>5876</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -12518,10 +12545,10 @@
         <v>1017</v>
       </c>
       <c r="H39">
-        <v>10677</v>
+        <v>1434</v>
       </c>
       <c r="I39">
-        <v>6009</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -12547,10 +12574,10 @@
         <v>1104</v>
       </c>
       <c r="H40">
-        <v>5946</v>
+        <v>1489</v>
       </c>
       <c r="I40">
-        <v>5790</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -12588,10 +12615,10 @@
         <v>24</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -12661,7 +12688,7 @@
       </c>
       <c r="H56">
         <f>AVERAGE(H14:H18)</f>
-        <v>498.2</v>
+        <v>458.2</v>
       </c>
       <c r="I56">
         <f>AVERAGE(I14:I18)</f>
@@ -12698,11 +12725,11 @@
       </c>
       <c r="H57">
         <f>AVERAGE(H25:H29)</f>
-        <v>732</v>
-      </c>
-      <c r="I57" t="e">
+        <v>792.2</v>
+      </c>
+      <c r="I57">
         <f>AVERAGE(I25:I29)</f>
-        <v>#DIV/0!</v>
+        <v>720.2</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -12735,11 +12762,11 @@
       </c>
       <c r="H58">
         <f>AVERAGE(H36:H40)</f>
-        <v>9273.6</v>
+        <v>1375</v>
       </c>
       <c r="I58">
         <f>AVERAGE(I36:I40)</f>
-        <v>5641.2</v>
+        <v>1270.5999999999999</v>
       </c>
     </row>
     <row r="65" spans="5:10" x14ac:dyDescent="0.25">
@@ -12750,13 +12777,13 @@
         <v>10</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I65" s="11" t="s">
         <v>32</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="5:10" x14ac:dyDescent="0.25">
@@ -12793,11 +12820,11 @@
         <v>0</v>
       </c>
       <c r="H67" s="12">
-        <f t="shared" ref="H67:H69" si="6">(G56 - H56) / G56</f>
-        <v>-0.44322132097334882</v>
+        <f>(G56 - H56) / G56</f>
+        <v>-0.32734646581691773</v>
       </c>
       <c r="I67" s="12">
-        <f t="shared" ref="I67:I69" si="7">(G56 - I56) / G56</f>
+        <f t="shared" ref="I67" si="6">(G56 - I56) / G56</f>
         <v>-0.12572421784472779</v>
       </c>
     </row>
@@ -12814,12 +12841,12 @@
         <v>0</v>
       </c>
       <c r="H68" s="12">
-        <f t="shared" si="6"/>
-        <v>-0.2107178299702282</v>
-      </c>
-      <c r="I68" s="12" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
+        <f>(G57 - H57) / G57</f>
+        <v>-0.31028779358253394</v>
+      </c>
+      <c r="I68" s="12">
+        <f>(G57 - I57) / G57</f>
+        <v>-0.19120079391333117</v>
       </c>
     </row>
     <row r="69" spans="5:10" x14ac:dyDescent="0.25">
@@ -12835,12 +12862,12 @@
         <v>0</v>
       </c>
       <c r="H69" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.8387342737323671</v>
+        <f t="shared" ref="H69" si="7">(G58 - H58) / G58</f>
+        <v>-0.31052230270682418</v>
       </c>
       <c r="I69" s="12">
-        <f t="shared" si="7"/>
-        <v>-4.3766679374761726</v>
+        <f>(G58 - I58) / G58</f>
+        <v>-0.21101791841402959</v>
       </c>
     </row>
   </sheetData>
@@ -12923,10 +12950,10 @@
         <v>24</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -13135,10 +13162,10 @@
         <v>24</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -13347,10 +13374,10 @@
         <v>24</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -13378,6 +13405,9 @@
       <c r="H24">
         <v>3.6419999999999999</v>
       </c>
+      <c r="I24">
+        <v>3.782</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -13401,6 +13431,12 @@
       <c r="G25">
         <v>1.1639999999999999</v>
       </c>
+      <c r="H25">
+        <v>3.8420000000000001</v>
+      </c>
+      <c r="I25">
+        <v>3.51</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -13424,6 +13460,12 @@
       <c r="G26">
         <v>1.304</v>
       </c>
+      <c r="H26">
+        <v>4.0060000000000002</v>
+      </c>
+      <c r="I26">
+        <v>3.8380000000000001</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -13447,6 +13489,12 @@
       <c r="G27">
         <v>1.5289999999999999</v>
       </c>
+      <c r="H27">
+        <v>3.8039999999999998</v>
+      </c>
+      <c r="I27">
+        <v>3.9449999999999998</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -13469,6 +13517,12 @@
       </c>
       <c r="G28">
         <v>1.244</v>
+      </c>
+      <c r="H28">
+        <v>3.9769999999999999</v>
+      </c>
+      <c r="I28">
+        <v>3.851</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -13517,10 +13571,10 @@
         <v>24</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -13546,7 +13600,7 @@
         <v>1.222</v>
       </c>
       <c r="H35">
-        <v>5.3860000000000001</v>
+        <v>3.742</v>
       </c>
       <c r="I35">
         <v>3.5619999999999998</v>
@@ -13575,7 +13629,7 @@
         <v>2.15</v>
       </c>
       <c r="H36">
-        <v>5.2069999999999999</v>
+        <v>3.8420000000000001</v>
       </c>
       <c r="I36">
         <v>3.8359999999999999</v>
@@ -13604,7 +13658,7 @@
         <v>1.5660000000000001</v>
       </c>
       <c r="H37">
-        <v>4.9720000000000004</v>
+        <v>4.0060000000000002</v>
       </c>
       <c r="I37">
         <v>3.5710000000000002</v>
@@ -13633,7 +13687,7 @@
         <v>1.401</v>
       </c>
       <c r="H38">
-        <v>5.4829999999999997</v>
+        <v>3.8039999999999998</v>
       </c>
       <c r="I38">
         <v>3.343</v>
@@ -13662,7 +13716,7 @@
         <v>1.7030000000000001</v>
       </c>
       <c r="H39">
-        <v>5.2750000000000004</v>
+        <v>3.9769999999999999</v>
       </c>
       <c r="I39">
         <v>3.5059999999999998</v>
@@ -13700,10 +13754,10 @@
         <v>10</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -13810,11 +13864,11 @@
       </c>
       <c r="H57">
         <f>AVERAGE(H24:H28)</f>
-        <v>3.6419999999999999</v>
-      </c>
-      <c r="I57" t="e">
+        <v>3.8542000000000001</v>
+      </c>
+      <c r="I57">
         <f>AVERAGE(I24:I28)</f>
-        <v>#DIV/0!</v>
+        <v>3.7851999999999997</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -13847,7 +13901,7 @@
       </c>
       <c r="H58">
         <f>AVERAGE(H35:H39)</f>
-        <v>5.2645999999999997</v>
+        <v>3.8741999999999996</v>
       </c>
       <c r="I58">
         <f>AVERAGE(I35:I39)</f>
@@ -13933,10 +13987,10 @@
         <v>24</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -14088,11 +14142,11 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -14158,11 +14212,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
@@ -14176,10 +14230,10 @@
         <v>24</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -14328,10 +14382,10 @@
         <v>24</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -14495,11 +14549,11 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
@@ -14516,10 +14570,10 @@
         <v>24</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -14639,7 +14693,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -14683,10 +14737,10 @@
         <v>24</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -14709,7 +14763,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>3.3500000000000002E-2</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -14729,7 +14783,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>3.9199999999999999E-2</v>
+        <v>0.2145</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -14749,7 +14803,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>3.3700000000000001E-2</v>
+        <v>0.26140000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -14769,7 +14823,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>2.98E-2</v>
+        <v>0.18403</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -14789,15 +14843,15 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>3.6600000000000001E-2</v>
+        <v>0.22450000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="8"/>
@@ -14814,10 +14868,10 @@
         <v>24</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -14837,7 +14891,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="5">
-        <v>2.6009999999999998E-2</v>
+        <v>0.26600000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -14857,7 +14911,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="5">
-        <v>4.027E-2</v>
+        <v>0.27950000000000003</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -14877,7 +14931,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="5">
-        <v>2.7080000000000003E-2</v>
+        <v>0.26419999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -14897,7 +14951,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="5">
-        <v>2.3740000000000001E-2</v>
+        <v>0.25958999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -14917,7 +14971,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="5">
-        <v>3.0540999999999999E-2</v>
+        <v>0.26369999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -14966,10 +15020,10 @@
         <v>24</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -14998,7 +15052,7 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>3.4209999999999997E-2</v>
+        <v>0.24210000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -15027,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>0.32500000000000001</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -15056,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>2.7199999999999998E-2</v>
+        <v>0.27200000000000002</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -15085,7 +15139,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>3.2099999999999997E-2</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -15114,15 +15168,15 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>3.4799999999999998E-2</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="18" t="s">
+      <c r="A75" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="8"/>
@@ -15139,10 +15193,10 @@
         <v>24</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -15162,7 +15216,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="5">
-        <v>4.1277000000000001E-2</v>
+        <v>0.19600000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -15182,7 +15236,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="5">
-        <v>4.3520000000000003E-2</v>
+        <v>0.2205</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -15202,7 +15256,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="5">
-        <v>3.1890000000000002E-2</v>
+        <v>0.2442</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -15222,7 +15276,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="5">
-        <v>2.4369999999999999E-2</v>
+        <v>0.20959</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -15242,7 +15296,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="5">
-        <v>4.4150000000000002E-2</v>
+        <v>0.23369999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -15285,10 +15339,10 @@
         <v>10</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -15348,7 +15402,7 @@
       </c>
       <c r="E91" s="12">
         <f>AVERAGE(I50:I54)</f>
-        <v>3.4559999999999994E-2</v>
+        <v>0.212426</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -15368,16 +15422,16 @@
       </c>
       <c r="E92" s="12">
         <f>AVERAGE(I69:I73)</f>
-        <v>9.0662000000000006E-2</v>
+        <v>0.24162</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="17" t="s">
+      <c r="A95" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="19"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
@@ -15390,10 +15444,10 @@
         <v>6</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -15464,7 +15518,7 @@
       </c>
       <c r="F99" s="5">
         <f>AVERAGE(F58:F62)</f>
-        <v>2.9528200000000004E-2</v>
+        <v>0.266598</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -15488,11 +15542,17 @@
       </c>
       <c r="F100" s="5">
         <f>AVERAGE(F77:F81)</f>
-        <v>3.7041400000000002E-2</v>
+        <v>0.22079799999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A75:C75"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -15503,12 +15563,6 @@
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A75:C75"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15578,10 +15632,10 @@
         <v>24</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -15790,10 +15844,10 @@
         <v>24</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -15958,7 +16012,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -16002,10 +16056,10 @@
         <v>24</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -16031,10 +16085,10 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>596</v>
+        <v>50</v>
       </c>
       <c r="I29">
-        <v>245</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -16060,10 +16114,10 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="I30">
-        <v>248</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -16089,10 +16143,10 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>434</v>
+        <v>142</v>
       </c>
       <c r="I31">
-        <v>206</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -16118,10 +16172,10 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>614</v>
+        <v>27</v>
       </c>
       <c r="I32">
-        <v>112</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -16147,10 +16201,10 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>400</v>
+        <v>41</v>
       </c>
       <c r="I33">
-        <v>222</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -16199,10 +16253,10 @@
         <v>24</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -16382,13 +16436,13 @@
         <v>10</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L50" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -16495,11 +16549,11 @@
       </c>
       <c r="H53">
         <f>AVERAGE(H29:H33)</f>
-        <v>476.6</v>
+        <v>59</v>
       </c>
       <c r="I53">
         <f>AVERAGE(I29:I33)</f>
-        <v>206.6</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -16548,10 +16602,10 @@
         <v>10</v>
       </c>
       <c r="K58" s="10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">

--- a/Experiments data/K Size/K_Size_4elt_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_4elt_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF155CEA-666B-4F01-95C6-FE3C5B71F9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9519144-CC35-44F9-8FBA-796B7C95D859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -116,16 +116,7 @@
     <t>Deep Multilevel, ε= 0.0</t>
   </si>
   <si>
-    <t>Deep Multilevel, ε = 0.05</t>
-  </si>
-  <si>
     <t>K = 8, Graph = 4elt, Contraction = 70%, Cardinality Sizes = [ 654, 850, 1105, 1437, 1868, 2429, 3157, 4106] at f = 0.3, CL= 2341</t>
-  </si>
-  <si>
-    <t>Deep Multilevel, ε = 5</t>
-  </si>
-  <si>
-    <t>Deep Multilevel, ε= 0</t>
   </si>
   <si>
     <t>(B2−C2)/B2</t>
@@ -141,6 +132,15 @@
   </si>
   <si>
     <t>Deep Multilevel, ε = 1561</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 50</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 780</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε= 0.0</t>
   </si>
 </sst>
 </file>
@@ -317,14 +317,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -677,13 +677,13 @@
                   <c:v>182.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>498.2</c:v>
+                  <c:v>458.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6317.6</c:v>
+                  <c:v>792.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9273.6</c:v>
+                  <c:v>1375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -773,10 +773,10 @@
                   <c:v>388.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3524.8</c:v>
+                  <c:v>720.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5641.2</c:v>
+                  <c:v>1270.5999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1703,7 +1703,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1763,13 +1763,13 @@
                   <c:v>-0.31936416184971089</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.44322132097334882</c:v>
+                  <c:v>-0.32734646581691773</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-9.4492226265299362</c:v>
+                  <c:v>-0.31028779358253394</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-7.8387342737323671</c:v>
+                  <c:v>-0.31052230270682418</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1790,7 +1790,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 780</c:v>
+                  <c:v>Deep NUGP, ε = 780</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1853,10 +1853,10 @@
                   <c:v>-0.12572421784472779</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-4.8299702282500832</c:v>
+                  <c:v>-0.19120079391333117</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-4.3766679374761726</c:v>
+                  <c:v>-0.21101791841402959</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1965,7 +1965,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1997,7 +1997,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -2464,16 +2464,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>40.6</c:v>
+                  <c:v>19.600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>164.4</c:v>
+                  <c:v>84</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>329.2</c:v>
+                  <c:v>107</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>333.4</c:v>
+                  <c:v>188.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2565,7 +2565,7 @@
                   <c:v>119</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>248</c:v>
+                  <c:v>180.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3480,7 +3480,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0.0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3549,10 +3549,10 @@
                   <c:v>3.0064000000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.8542000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.2645999999999997</c:v>
+                  <c:v>3.8741999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3573,7 +3573,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 0.05</c:v>
+                  <c:v>Deep NUGP, ε = 780</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3642,7 +3642,7 @@
                   <c:v>3.2231999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.7851999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3.5635999999999997</c:v>
@@ -4680,7 +4680,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep Multilevel, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4767,7 +4767,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep Multilevel, ε = 780</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4830,10 +4830,10 @@
                   <c:v>8.8782E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9528200000000004E-2</c:v>
+                  <c:v>0.266598</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.7041400000000002E-2</c:v>
+                  <c:v>0.22079799999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5504,7 +5504,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep NUGP, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5591,7 +5591,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 780</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5654,10 +5654,10 @@
                   <c:v>7.8972000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.4559999999999994E-2</c:v>
+                  <c:v>0.212426</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.0662000000000006E-2</c:v>
+                  <c:v>0.24162</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6225,7 +6225,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep Multilevel, ε= 0.0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6294,7 +6294,7 @@
                   <c:v>4.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>476.6</c:v>
+                  <c:v>59</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>598.4</c:v>
@@ -6318,7 +6318,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep Multilevel, ε = 780</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6387,7 +6387,7 @@
                   <c:v>4.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>206.6</c:v>
+                  <c:v>31.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>343.4</c:v>
@@ -11056,16 +11056,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>119061</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>52386</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11356,7 +11356,7 @@
             <v>2</v>
           </cell>
           <cell r="H51">
-            <v>40.6</v>
+            <v>19.600000000000001</v>
           </cell>
           <cell r="I51">
             <v>27.8</v>
@@ -11385,7 +11385,7 @@
             <v>11.8</v>
           </cell>
           <cell r="H52">
-            <v>164.4</v>
+            <v>84</v>
           </cell>
           <cell r="I52">
             <v>40.799999999999997</v>
@@ -11414,7 +11414,7 @@
             <v>16</v>
           </cell>
           <cell r="H53">
-            <v>329.2</v>
+            <v>107</v>
           </cell>
           <cell r="I53">
             <v>119</v>
@@ -11443,10 +11443,10 @@
             <v>78.8</v>
           </cell>
           <cell r="H54">
-            <v>333.4</v>
+            <v>188.4</v>
           </cell>
           <cell r="I54">
-            <v>248</v>
+            <v>180.4</v>
           </cell>
         </row>
       </sheetData>
@@ -11767,7 +11767,7 @@
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
       <c r="I1" s="13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -11781,7 +11781,7 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11808,10 +11808,10 @@
         <v>24</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -12020,10 +12020,10 @@
         <v>24</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -12113,7 +12113,7 @@
         <v>342</v>
       </c>
       <c r="H16">
-        <v>623</v>
+        <v>423</v>
       </c>
       <c r="I16">
         <v>435</v>
@@ -12188,7 +12188,7 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -12232,10 +12232,10 @@
         <v>24</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -12261,10 +12261,10 @@
         <v>604</v>
       </c>
       <c r="H25">
-        <v>7354</v>
+        <v>750</v>
       </c>
       <c r="I25">
-        <v>4490</v>
+        <v>708</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -12290,10 +12290,10 @@
         <v>586</v>
       </c>
       <c r="H26">
-        <v>5805</v>
+        <v>782</v>
       </c>
       <c r="I26">
-        <v>3772</v>
+        <v>737</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -12319,10 +12319,10 @@
         <v>584</v>
       </c>
       <c r="H27">
-        <v>6699</v>
+        <v>805</v>
       </c>
       <c r="I27">
-        <v>3379</v>
+        <v>670</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -12348,10 +12348,10 @@
         <v>649</v>
       </c>
       <c r="H28">
-        <v>6266</v>
+        <v>814</v>
       </c>
       <c r="I28">
-        <v>3912</v>
+        <v>601</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -12377,10 +12377,10 @@
         <v>600</v>
       </c>
       <c r="H29">
-        <v>5464</v>
+        <v>810</v>
       </c>
       <c r="I29">
-        <v>2071</v>
+        <v>885</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -12429,10 +12429,10 @@
         <v>24</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -12458,10 +12458,10 @@
         <v>1081</v>
       </c>
       <c r="H36">
-        <v>10599</v>
+        <v>1236</v>
       </c>
       <c r="I36">
-        <v>5162</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -12487,10 +12487,10 @@
         <v>984</v>
       </c>
       <c r="H37">
-        <v>8325</v>
+        <v>1336</v>
       </c>
       <c r="I37">
-        <v>5369</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -12516,10 +12516,10 @@
         <v>1060</v>
       </c>
       <c r="H38">
-        <v>10821</v>
+        <v>1380</v>
       </c>
       <c r="I38">
-        <v>5876</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -12545,10 +12545,10 @@
         <v>1017</v>
       </c>
       <c r="H39">
-        <v>10677</v>
+        <v>1434</v>
       </c>
       <c r="I39">
-        <v>6009</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -12574,10 +12574,10 @@
         <v>1104</v>
       </c>
       <c r="H40">
-        <v>5946</v>
+        <v>1489</v>
       </c>
       <c r="I40">
-        <v>5790</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -12615,10 +12615,10 @@
         <v>24</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H56">
         <f>AVERAGE(H14:H18)</f>
-        <v>498.2</v>
+        <v>458.2</v>
       </c>
       <c r="I56">
         <f>AVERAGE(I14:I18)</f>
@@ -12725,11 +12725,11 @@
       </c>
       <c r="H57">
         <f>AVERAGE(H25:H29)</f>
-        <v>6317.6</v>
+        <v>792.2</v>
       </c>
       <c r="I57">
         <f>AVERAGE(I25:I29)</f>
-        <v>3524.8</v>
+        <v>720.2</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -12762,11 +12762,11 @@
       </c>
       <c r="H58">
         <f>AVERAGE(H36:H40)</f>
-        <v>9273.6</v>
+        <v>1375</v>
       </c>
       <c r="I58">
         <f>AVERAGE(I36:I40)</f>
-        <v>5641.2</v>
+        <v>1270.5999999999999</v>
       </c>
     </row>
     <row r="65" spans="5:10" x14ac:dyDescent="0.25">
@@ -12777,13 +12777,13 @@
         <v>10</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I65" s="11" t="s">
         <v>32</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="5:10" x14ac:dyDescent="0.25">
@@ -12820,11 +12820,11 @@
         <v>0</v>
       </c>
       <c r="H67" s="12">
-        <f t="shared" ref="H67:H69" si="6">(G56 - H56) / G56</f>
-        <v>-0.44322132097334882</v>
+        <f>(G56 - H56) / G56</f>
+        <v>-0.32734646581691773</v>
       </c>
       <c r="I67" s="12">
-        <f t="shared" ref="I67:I69" si="7">(G56 - I56) / G56</f>
+        <f t="shared" ref="I67" si="6">(G56 - I56) / G56</f>
         <v>-0.12572421784472779</v>
       </c>
     </row>
@@ -12841,12 +12841,12 @@
         <v>0</v>
       </c>
       <c r="H68" s="12">
-        <f t="shared" si="6"/>
-        <v>-9.4492226265299362</v>
+        <f>(G57 - H57) / G57</f>
+        <v>-0.31028779358253394</v>
       </c>
       <c r="I68" s="12">
-        <f t="shared" si="7"/>
-        <v>-4.8299702282500832</v>
+        <f>(G57 - I57) / G57</f>
+        <v>-0.19120079391333117</v>
       </c>
     </row>
     <row r="69" spans="5:10" x14ac:dyDescent="0.25">
@@ -12862,12 +12862,12 @@
         <v>0</v>
       </c>
       <c r="H69" s="12">
-        <f t="shared" si="6"/>
-        <v>-7.8387342737323671</v>
+        <f t="shared" ref="H69" si="7">(G58 - H58) / G58</f>
+        <v>-0.31052230270682418</v>
       </c>
       <c r="I69" s="12">
-        <f t="shared" si="7"/>
-        <v>-4.3766679374761726</v>
+        <f>(G58 - I58) / G58</f>
+        <v>-0.21101791841402959</v>
       </c>
     </row>
   </sheetData>
@@ -12950,10 +12950,10 @@
         <v>24</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -13162,10 +13162,10 @@
         <v>24</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -13374,10 +13374,10 @@
         <v>24</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -13402,6 +13402,12 @@
       <c r="G24">
         <v>0.85599999999999998</v>
       </c>
+      <c r="H24">
+        <v>3.6419999999999999</v>
+      </c>
+      <c r="I24">
+        <v>3.782</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -13425,6 +13431,12 @@
       <c r="G25">
         <v>1.1639999999999999</v>
       </c>
+      <c r="H25">
+        <v>3.8420000000000001</v>
+      </c>
+      <c r="I25">
+        <v>3.51</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -13448,6 +13460,12 @@
       <c r="G26">
         <v>1.304</v>
       </c>
+      <c r="H26">
+        <v>4.0060000000000002</v>
+      </c>
+      <c r="I26">
+        <v>3.8380000000000001</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -13471,6 +13489,12 @@
       <c r="G27">
         <v>1.5289999999999999</v>
       </c>
+      <c r="H27">
+        <v>3.8039999999999998</v>
+      </c>
+      <c r="I27">
+        <v>3.9449999999999998</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -13493,6 +13517,12 @@
       </c>
       <c r="G28">
         <v>1.244</v>
+      </c>
+      <c r="H28">
+        <v>3.9769999999999999</v>
+      </c>
+      <c r="I28">
+        <v>3.851</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -13541,10 +13571,10 @@
         <v>24</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -13570,7 +13600,7 @@
         <v>1.222</v>
       </c>
       <c r="H35">
-        <v>5.3860000000000001</v>
+        <v>3.742</v>
       </c>
       <c r="I35">
         <v>3.5619999999999998</v>
@@ -13599,7 +13629,7 @@
         <v>2.15</v>
       </c>
       <c r="H36">
-        <v>5.2069999999999999</v>
+        <v>3.8420000000000001</v>
       </c>
       <c r="I36">
         <v>3.8359999999999999</v>
@@ -13628,7 +13658,7 @@
         <v>1.5660000000000001</v>
       </c>
       <c r="H37">
-        <v>4.9720000000000004</v>
+        <v>4.0060000000000002</v>
       </c>
       <c r="I37">
         <v>3.5710000000000002</v>
@@ -13657,7 +13687,7 @@
         <v>1.401</v>
       </c>
       <c r="H38">
-        <v>5.4829999999999997</v>
+        <v>3.8039999999999998</v>
       </c>
       <c r="I38">
         <v>3.343</v>
@@ -13686,7 +13716,7 @@
         <v>1.7030000000000001</v>
       </c>
       <c r="H39">
-        <v>5.2750000000000004</v>
+        <v>3.9769999999999999</v>
       </c>
       <c r="I39">
         <v>3.5059999999999998</v>
@@ -13724,10 +13754,10 @@
         <v>10</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -13832,13 +13862,13 @@
         <f t="shared" si="2"/>
         <v>1.2193999999999998</v>
       </c>
-      <c r="H57" t="e">
+      <c r="H57">
         <f>AVERAGE(H24:H28)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I57" t="e">
+        <v>3.8542000000000001</v>
+      </c>
+      <c r="I57">
         <f>AVERAGE(I24:I28)</f>
-        <v>#DIV/0!</v>
+        <v>3.7851999999999997</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -13871,7 +13901,7 @@
       </c>
       <c r="H58">
         <f>AVERAGE(H35:H39)</f>
-        <v>5.2645999999999997</v>
+        <v>3.8741999999999996</v>
       </c>
       <c r="I58">
         <f>AVERAGE(I35:I39)</f>
@@ -13957,10 +13987,10 @@
         <v>24</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J3" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -14112,11 +14142,11 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -14182,11 +14212,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
@@ -14200,10 +14230,10 @@
         <v>24</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -14352,10 +14382,10 @@
         <v>24</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -14519,11 +14549,11 @@
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
@@ -14540,10 +14570,10 @@
         <v>24</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -14663,7 +14693,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -14707,10 +14737,10 @@
         <v>24</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -14733,7 +14763,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>3.3500000000000002E-2</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -14753,7 +14783,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>3.9199999999999999E-2</v>
+        <v>0.2145</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -14773,7 +14803,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>3.3700000000000001E-2</v>
+        <v>0.26140000000000002</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -14793,7 +14823,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>2.98E-2</v>
+        <v>0.18403</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -14813,15 +14843,15 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>3.6600000000000001E-2</v>
+        <v>0.22450000000000001</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
+      <c r="A56" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B56" s="18"/>
-      <c r="C56" s="18"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="8"/>
@@ -14838,10 +14868,10 @@
         <v>24</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
@@ -14861,7 +14891,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="5">
-        <v>2.6009999999999998E-2</v>
+        <v>0.26600000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
@@ -14881,7 +14911,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="5">
-        <v>4.027E-2</v>
+        <v>0.27950000000000003</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
@@ -14901,7 +14931,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="5">
-        <v>2.7080000000000003E-2</v>
+        <v>0.26419999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
@@ -14921,7 +14951,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="5">
-        <v>2.3740000000000001E-2</v>
+        <v>0.25958999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -14941,7 +14971,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="5">
-        <v>3.0540999999999999E-2</v>
+        <v>0.26369999999999999</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
@@ -14990,10 +15020,10 @@
         <v>24</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
@@ -15022,7 +15052,7 @@
         <v>0</v>
       </c>
       <c r="I69">
-        <v>3.4209999999999997E-2</v>
+        <v>0.24210000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
@@ -15051,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>0.32500000000000001</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
@@ -15080,7 +15110,7 @@
         <v>0</v>
       </c>
       <c r="I71">
-        <v>2.7199999999999998E-2</v>
+        <v>0.27200000000000002</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
@@ -15109,7 +15139,7 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>3.2099999999999997E-2</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
@@ -15138,15 +15168,15 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>3.4799999999999998E-2</v>
+        <v>0.248</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="18" t="s">
+      <c r="A75" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B75" s="18"/>
-      <c r="C75" s="18"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="8"/>
@@ -15163,10 +15193,10 @@
         <v>24</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
@@ -15186,7 +15216,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="5">
-        <v>4.1277000000000001E-2</v>
+        <v>0.19600000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
@@ -15206,7 +15236,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="5">
-        <v>4.3520000000000003E-2</v>
+        <v>0.2205</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
@@ -15226,7 +15256,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="5">
-        <v>3.1890000000000002E-2</v>
+        <v>0.2442</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
@@ -15246,7 +15276,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="5">
-        <v>2.4369999999999999E-2</v>
+        <v>0.20959</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -15266,7 +15296,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="5">
-        <v>4.4150000000000002E-2</v>
+        <v>0.23369999999999999</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -15309,10 +15339,10 @@
         <v>10</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -15372,7 +15402,7 @@
       </c>
       <c r="E91" s="12">
         <f>AVERAGE(I50:I54)</f>
-        <v>3.4559999999999994E-2</v>
+        <v>0.212426</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -15392,16 +15422,16 @@
       </c>
       <c r="E92" s="12">
         <f>AVERAGE(I69:I73)</f>
-        <v>9.0662000000000006E-2</v>
+        <v>0.24162</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="17" t="s">
+      <c r="A95" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
+      <c r="B95" s="19"/>
+      <c r="C95" s="19"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
@@ -15414,10 +15444,10 @@
         <v>6</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -15488,7 +15518,7 @@
       </c>
       <c r="F99" s="5">
         <f>AVERAGE(F58:F62)</f>
-        <v>2.9528200000000004E-2</v>
+        <v>0.266598</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -15512,11 +15542,17 @@
       </c>
       <c r="F100" s="5">
         <f>AVERAGE(F77:F81)</f>
-        <v>3.7041400000000002E-2</v>
+        <v>0.22079799999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A75:C75"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -15527,12 +15563,6 @@
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A87:G87"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A75:C75"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15602,10 +15632,10 @@
         <v>24</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -15814,10 +15844,10 @@
         <v>24</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -15982,7 +16012,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -16026,10 +16056,10 @@
         <v>24</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -16055,10 +16085,10 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>596</v>
+        <v>50</v>
       </c>
       <c r="I29">
-        <v>245</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -16084,10 +16114,10 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>339</v>
+        <v>35</v>
       </c>
       <c r="I30">
-        <v>248</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -16113,10 +16143,10 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>434</v>
+        <v>142</v>
       </c>
       <c r="I31">
-        <v>206</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -16142,10 +16172,10 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>614</v>
+        <v>27</v>
       </c>
       <c r="I32">
-        <v>112</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -16171,10 +16201,10 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>400</v>
+        <v>41</v>
       </c>
       <c r="I33">
-        <v>222</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -16223,10 +16253,10 @@
         <v>24</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -16406,13 +16436,13 @@
         <v>10</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L50" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -16519,11 +16549,11 @@
       </c>
       <c r="H53">
         <f>AVERAGE(H29:H33)</f>
-        <v>476.6</v>
+        <v>59</v>
       </c>
       <c r="I53">
         <f>AVERAGE(I29:I33)</f>
-        <v>206.6</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -16572,10 +16602,10 @@
         <v>10</v>
       </c>
       <c r="K58" s="10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">

--- a/Experiments data/K Size/K_Size_4elt_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_4elt_Graph.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9519144-CC35-44F9-8FBA-796B7C95D859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815746E5-416E-4A88-A653-AAF26A1CC58F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="35">
   <si>
     <t>KaMinPar</t>
   </si>
@@ -137,10 +137,13 @@
     <t>Deep Multilevel, ε = 50</t>
   </si>
   <si>
-    <t>Deep NUGP, ε = 780</t>
+    <t>Deep NUGP, ε= 0.0</t>
   </si>
   <si>
-    <t>Deep NUGP, ε= 0.0</t>
+    <t>Deep Multilevel, ε relaxed</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε relaxed</t>
   </si>
 </sst>
 </file>
@@ -1790,7 +1793,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 780</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1965,7 +1968,7 @@
         <c:title>
           <c:tx>
             <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
@@ -1983,7 +1986,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US" sz="1800"/>
-                  <a:t>% of Improvment</a:t>
+                  <a:t>Precentage of Improvment</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1997,7 +2000,7 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
@@ -3573,7 +3576,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 780</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4767,7 +4770,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 780</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5591,7 +5594,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep NUGP, ε = 780</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6318,7 +6321,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 780</c:v>
+                  <c:v>Deep NUGP, ε relaxed</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11176,16 +11179,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>331133</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>131388</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>308723</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>8124</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>997323</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>145676</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -11212,16 +11215,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2028264</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>25493</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>582705</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>148757</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>89647</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>33618</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>403412</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>156882</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12777,10 +12780,10 @@
         <v>10</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>30</v>
@@ -13754,10 +13757,10 @@
         <v>10</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
@@ -15339,10 +15342,10 @@
         <v>10</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -15447,7 +15450,7 @@
         <v>24</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -16439,7 +16442,7 @@
         <v>24</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L50" t="s">
         <v>26</v>
@@ -16605,7 +16608,7 @@
         <v>24</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">

--- a/Experiments data/K Size/K_Size_4elt_Graph.xlsx
+++ b/Experiments data/K Size/K_Size_4elt_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\K Size\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9519144-CC35-44F9-8FBA-796B7C95D859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550A0A91-3104-4C99-BD18-857D63584759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="34">
   <si>
     <t>KaMinPar</t>
   </si>
@@ -11103,8 +11103,8 @@
       <xdr:rowOff>122465</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>559936</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>82</xdr:row>
       <xdr:rowOff>136754</xdr:rowOff>
     </xdr:to>
@@ -12890,7 +12890,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
@@ -13722,7 +13722,73 @@
         <v>3.5059999999999998</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M49" s="2"/>
+      <c r="N49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="P49" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q49" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M50" s="1">
+        <v>2</v>
+      </c>
+      <c r="N50">
+        <v>1.4762</v>
+      </c>
+      <c r="O50">
+        <v>0.98839999999999983</v>
+      </c>
+      <c r="P50">
+        <v>2.508</v>
+      </c>
+      <c r="Q50">
+        <v>2.3768000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M51" s="1">
+        <v>4</v>
+      </c>
+      <c r="N51">
+        <v>2.0864000000000003</v>
+      </c>
+      <c r="O51">
+        <v>1.0564</v>
+      </c>
+      <c r="P51">
+        <v>3.0064000000000002</v>
+      </c>
+      <c r="Q51">
+        <v>3.2231999999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="M52" s="1">
+        <v>8</v>
+      </c>
+      <c r="N52">
+        <v>2.1432000000000002</v>
+      </c>
+      <c r="O52">
+        <v>1.2193999999999998</v>
+      </c>
+      <c r="P52">
+        <v>3.8542000000000001</v>
+      </c>
+      <c r="Q52">
+        <v>3.7851999999999997</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="16" t="s">
         <v>22</v>
       </c>
@@ -13732,8 +13798,23 @@
       <c r="E53" s="16"/>
       <c r="F53" s="16"/>
       <c r="G53" s="16"/>
-    </row>
-    <row r="54" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="M53" s="1">
+        <v>16</v>
+      </c>
+      <c r="N53">
+        <v>2.9089999999999998</v>
+      </c>
+      <c r="O53">
+        <v>1.6084000000000001</v>
+      </c>
+      <c r="P53">
+        <v>3.8741999999999996</v>
+      </c>
+      <c r="Q53">
+        <v>3.5635999999999997</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="1" t="s">
         <v>6</v>
@@ -13760,7 +13841,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>2</v>
       </c>
@@ -13797,7 +13878,7 @@
         <v>2.3768000000000002</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>4</v>
       </c>
@@ -13834,7 +13915,7 @@
         <v>3.2231999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>8</v>
       </c>
@@ -13871,7 +13952,7 @@
         <v>3.7851999999999997</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>16</v>
       </c>
